--- a/data/trans_dic/P57_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Provincia-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,65; 37,29</t>
+          <t>26,11; 37,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,17; 34,08</t>
+          <t>19,06; 34,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 31,05</t>
+          <t>20,49; 31,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,37; 20,99</t>
+          <t>13,41; 20,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,82; 32,44</t>
+          <t>24,4; 31,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,15; 25,98</t>
+          <t>17,4; 26,09</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 39,1</t>
+          <t>31,13; 39,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,66; 77,54</t>
+          <t>67,54; 78,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,83; 36,3</t>
+          <t>28,2; 36,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,01; 71,4</t>
+          <t>64,24; 71,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,59; 36,21</t>
+          <t>30,7; 36,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,94; 73,24</t>
+          <t>67,24; 73,3</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,53; 35,25</t>
+          <t>25,38; 35,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,39; 53,87</t>
+          <t>42,46; 53,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,29; 33,92</t>
+          <t>23,58; 33,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,16; 43,42</t>
+          <t>34,41; 43,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,03; 32,9</t>
+          <t>26,6; 33,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,74; 47,15</t>
+          <t>39,82; 46,69</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,51; 45,77</t>
+          <t>35,72; 46,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>32,88; 48,45</t>
+          <t>33,94; 47,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,83; 39,8</t>
+          <t>30,26; 40,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,87; 40,99</t>
+          <t>19,52; 41,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,19; 41,32</t>
+          <t>34,12; 41,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,94; 41,79</t>
+          <t>25,9; 42,01</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 20,81</t>
+          <t>11,24; 21,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,18; 46,58</t>
+          <t>34,27; 46,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,88; 16,35</t>
+          <t>7,87; 16,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,48; 41,03</t>
+          <t>31,51; 41,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,59; 16,81</t>
+          <t>10,5; 17,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,13; 42,09</t>
+          <t>33,96; 41,6</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45,38; 57,28</t>
+          <t>45,16; 57,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,68; 55,56</t>
+          <t>44,95; 55,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,33; 50,89</t>
+          <t>38,89; 50,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,75; 57,38</t>
+          <t>47,16; 56,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,94; 52,49</t>
+          <t>43,83; 52,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,09; 54,85</t>
+          <t>47,66; 55,19</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,24; 32,99</t>
+          <t>25,8; 33,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,0; 49,78</t>
+          <t>39,93; 49,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,42; 29,24</t>
+          <t>22,58; 29,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,75; 40,94</t>
+          <t>14,82; 40,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,99; 30,19</t>
+          <t>25,12; 30,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,85; 42,91</t>
+          <t>23,19; 43,22</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,23; 23,1</t>
+          <t>17,21; 23,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,37; 81,2</t>
+          <t>40,3; 81,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,55; 18,91</t>
+          <t>13,44; 19,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,83; 36,4</t>
+          <t>30,15; 36,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,96; 19,82</t>
+          <t>15,96; 20,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,76; 66,07</t>
+          <t>36,53; 67,0</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,9; 32,18</t>
+          <t>28,92; 32,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46,31; 62,22</t>
+          <t>46,32; 61,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,82</t>
+          <t>24,88; 27,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30,84; 41,11</t>
+          <t>30,17; 40,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,15; 29,37</t>
+          <t>27,22; 29,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,66; 50,15</t>
+          <t>40,55; 50,22</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10)</t>
+          <t>Población con autopercepción de la felicidad mayor o igual a 9 (Likert 0 a 10) (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75110; 109207</t>
+          <t>76465; 109255</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59714; 106144</t>
+          <t>59348; 106358</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59801; 89647</t>
+          <t>59161; 89848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38714; 60801</t>
+          <t>38830; 58327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>144323; 188647</t>
+          <t>141889; 185174</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>103074; 156153</t>
+          <t>104605; 156847</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>152780; 195248</t>
+          <t>155448; 197208</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>345545; 401959</t>
+          <t>350128; 405169</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>145018; 189207</t>
+          <t>146978; 187656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>327240; 365006</t>
+          <t>328434; 365123</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>312185; 369588</t>
+          <t>313331; 372590</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>689198; 754058</t>
+          <t>692270; 754677</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81098; 111988</t>
+          <t>80636; 113537</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133236; 169307</t>
+          <t>133450; 169460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81703; 114060</t>
+          <t>79300; 112604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>118722; 150894</t>
+          <t>119592; 150661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>170207; 215186</t>
+          <t>173959; 217388</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>263005; 312089</t>
+          <t>263542; 309015</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130310; 167967</t>
+          <t>131079; 169820</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100462; 148002</t>
+          <t>103676; 146194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114795; 153179</t>
+          <t>116445; 155840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92379; 190609</t>
+          <t>90758; 191870</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>257044; 310614</t>
+          <t>256485; 310108</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>199866; 321970</t>
+          <t>199586; 323680</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22818; 43960</t>
+          <t>23733; 44669</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61092; 83253</t>
+          <t>61263; 83982</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17229; 35739</t>
+          <t>17213; 36748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65076; 84817</t>
+          <t>65143; 85447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45526; 72254</t>
+          <t>45135; 74243</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>131544; 162229</t>
+          <t>130882; 160336</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>119417; 150711</t>
+          <t>118815; 150714</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120461; 149822</t>
+          <t>121203; 150571</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>107034; 138484</t>
+          <t>105831; 138593</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>120023; 147317</t>
+          <t>121080; 145068</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>235175; 280964</t>
+          <t>234621; 281272</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>247846; 288717</t>
+          <t>250854; 290526</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>164291; 214770</t>
+          <t>167918; 218439</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>249438; 310386</t>
+          <t>248984; 308523</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152960; 199505</t>
+          <t>154068; 202475</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>108014; 346955</t>
+          <t>125589; 344202</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>333191; 402461</t>
+          <t>334891; 400613</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>291951; 631180</t>
+          <t>341078; 635691</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>134154; 179817</t>
+          <t>133959; 183022</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>374649; 753612</t>
+          <t>374026; 758517</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>111643; 155809</t>
+          <t>110743; 157306</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>213635; 260629</t>
+          <t>215928; 264074</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>255758; 317612</t>
+          <t>255822; 323913</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>604398; 1086292</t>
+          <t>600644; 1101666</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>977133; 1087918</t>
+          <t>977737; 1087075</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1597551; 2146360</t>
+          <t>1598032; 2134364</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>877663; 981482</t>
+          <t>877838; 976656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1122807; 1496713</t>
+          <t>1098223; 1489538</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1875864; 2028846</t>
+          <t>1880581; 2033723</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2883072; 3555898</t>
+          <t>2875021; 3560702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P57_R2-Provincia-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,11; 37,31</t>
+          <t>25,39; 36,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 34,15</t>
+          <t>18,9; 28,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,49; 31,12</t>
+          <t>20,25; 31,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,41; 20,14</t>
+          <t>14,95; 23,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,4; 31,84</t>
+          <t>24,93; 32,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,4; 26,09</t>
+          <t>17,91; 24,26</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 39,49</t>
+          <t>30,95; 39,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,54; 78,16</t>
+          <t>67,93; 77,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,2; 36,01</t>
+          <t>28,24; 36,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64,24; 71,42</t>
+          <t>64,84; 71,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,7; 36,51</t>
+          <t>30,47; 36,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,24; 73,3</t>
+          <t>67,67; 73,46</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,91%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,38; 35,74</t>
+          <t>25,97; 35,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,46; 53,92</t>
+          <t>41,57; 52,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,58; 33,48</t>
+          <t>24,46; 33,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,41; 43,35</t>
+          <t>34,84; 43,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,6; 33,24</t>
+          <t>26,38; 33,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,82; 46,69</t>
+          <t>39,35; 46,43</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,72; 46,28</t>
+          <t>35,5; 45,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,94; 47,85</t>
+          <t>35,2; 49,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 40,49</t>
+          <t>30,66; 39,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,52; 41,26</t>
+          <t>35,87; 45,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,12; 41,25</t>
+          <t>34,23; 41,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,9; 42,01</t>
+          <t>37,92; 45,99</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,24; 21,15</t>
+          <t>10,55; 20,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,27; 46,98</t>
+          <t>34,86; 46,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 16,81</t>
+          <t>8,0; 16,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,51; 41,34</t>
+          <t>30,99; 40,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,5; 17,27</t>
+          <t>10,63; 17,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,96; 41,6</t>
+          <t>34,19; 41,78</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>45,16; 57,28</t>
+          <t>45,26; 57,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,95; 55,84</t>
+          <t>43,7; 54,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,89; 50,93</t>
+          <t>39,16; 51,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47,16; 56,5</t>
+          <t>46,62; 56,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,83; 52,55</t>
+          <t>44,04; 52,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,66; 55,19</t>
+          <t>46,54; 53,69</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,8; 33,56</t>
+          <t>25,57; 33,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>39,93; 49,48</t>
+          <t>39,91; 48,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22,58; 29,68</t>
+          <t>22,65; 29,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14,82; 40,62</t>
+          <t>36,47; 42,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,12; 30,05</t>
+          <t>25,2; 30,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,19; 43,22</t>
+          <t>38,85; 44,32</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,21; 23,51</t>
+          <t>16,9; 22,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,3; 81,73</t>
+          <t>38,13; 45,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,44; 19,09</t>
+          <t>13,54; 19,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30,15; 36,88</t>
+          <t>30,19; 36,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,96; 20,21</t>
+          <t>16,18; 20,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,53; 67,0</t>
+          <t>34,9; 39,97</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28,92; 32,15</t>
+          <t>28,83; 31,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46,32; 61,87</t>
+          <t>44,43; 48,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24,88; 27,68</t>
+          <t>24,87; 28,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30,17; 40,92</t>
+          <t>39,66; 42,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>27,22; 29,44</t>
+          <t>27,24; 29,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,55; 50,22</t>
+          <t>42,54; 44,93</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>74292</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48153</t>
+          <t>58333</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>132625</t>
         </is>
       </c>
     </row>
@@ -1506,32 +1506,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>76465; 109255</t>
+          <t>74348; 108149</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>59348; 106358</t>
+          <t>60256; 91544</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>59161; 89848</t>
+          <t>58460; 89516</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38830; 58327</t>
+          <t>47255; 72717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>141889; 185174</t>
+          <t>144994; 188331</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>104605; 156847</t>
+          <t>113680; 154046</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>377911</t>
+          <t>387517</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>346851</t>
+          <t>370494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>724761</t>
+          <t>758010</t>
         </is>
       </c>
     </row>
@@ -1624,32 +1624,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>155448; 197208</t>
+          <t>154531; 197942</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350128; 405169</t>
+          <t>360461; 412586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146978; 187656</t>
+          <t>147191; 190805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>328434; 365123</t>
+          <t>351833; 389548</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>313331; 372590</t>
+          <t>310977; 368793</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>692270; 754677</t>
+          <t>726343; 788415</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>151302</t>
+          <t>148938</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134552</t>
+          <t>138144</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>285854</t>
+          <t>287081</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80636; 113537</t>
+          <t>82497; 114064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133450; 169460</t>
+          <t>130659; 164467</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79300; 112604</t>
+          <t>82247; 113066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119592; 150661</t>
+          <t>123589; 154908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>173959; 217388</t>
+          <t>172554; 218144</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>263542; 309015</t>
+          <t>263263; 310656</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>123748</t>
+          <t>155158</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150976</t>
+          <t>168107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>274724</t>
+          <t>323265</t>
         </is>
       </c>
     </row>
@@ -1860,32 +1860,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131079; 169820</t>
+          <t>130263; 165676</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>103676; 146194</t>
+          <t>128598; 182489</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116445; 155840</t>
+          <t>118011; 153730</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90758; 191870</t>
+          <t>147009; 188247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>256485; 310108</t>
+          <t>257335; 309189</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>199586; 323680</t>
+          <t>293995; 356564</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71973</t>
+          <t>83706</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74388</t>
+          <t>80648</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>164354</t>
         </is>
       </c>
     </row>
@@ -1978,32 +1978,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23733; 44669</t>
+          <t>22290; 44112</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61263; 83982</t>
+          <t>71697; 95586</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17213; 36748</t>
+          <t>17486; 35513</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65143; 85447</t>
+          <t>70153; 91377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>45135; 74243</t>
+          <t>45672; 73900</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>130882; 160336</t>
+          <t>147706; 180508</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>135460</t>
+          <t>133138</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>133624</t>
+          <t>135785</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>269084</t>
+          <t>268923</t>
         </is>
       </c>
     </row>
@@ -2096,32 +2096,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>118815; 150714</t>
+          <t>119084; 150573</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>121203; 150571</t>
+          <t>118287; 147328</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>105831; 138593</t>
+          <t>106550; 138818</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>121080; 145068</t>
+          <t>122813; 147924</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>234621; 281272</t>
+          <t>235697; 279730</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>250854; 290526</t>
+          <t>248590; 286763</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>278005</t>
+          <t>317626</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254352</t>
+          <t>303921</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>532357</t>
+          <t>621547</t>
         </is>
       </c>
     </row>
@@ -2214,32 +2214,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>167918; 218439</t>
+          <t>166432; 217299</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>248984; 308523</t>
+          <t>286878; 346593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>154068; 202475</t>
+          <t>154530; 202066</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>125589; 344202</t>
+          <t>280853; 329353</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>334891; 400613</t>
+          <t>335914; 406558</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>341078; 635691</t>
+          <t>578466; 659844</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>529459</t>
+          <t>334011</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>275644</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>767948</t>
+          <t>609655</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133959; 183022</t>
+          <t>131543; 178313</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>374026; 758517</t>
+          <t>304079; 364776</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>110743; 157306</t>
+          <t>111565; 158118</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>215928; 264074</t>
+          <t>250436; 301501</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>255822; 323913</t>
+          <t>259260; 321139</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>600644; 1101666</t>
+          <t>567755; 650364</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2417,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1747144</t>
+          <t>1634384</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1381383</t>
+          <t>1531076</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3128528</t>
+          <t>3165460</t>
         </is>
       </c>
     </row>
@@ -2450,32 +2450,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>977737; 1087075</t>
+          <t>974570; 1080195</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1598032; 2134364</t>
+          <t>1564810; 1698228</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>877838; 976656</t>
+          <t>877364; 988351</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1098223; 1489538</t>
+          <t>1472474; 1587964</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1880581; 2033723</t>
+          <t>1881644; 2035801</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2875021; 3560702</t>
+          <t>3077618; 3250344</t>
         </is>
       </c>
     </row>
